--- a/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N22_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T12594_W0065F0003T0006Z000C1N22_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.71694209175066</v>
+        <v>5.479003089909482</v>
       </c>
       <c r="D2" t="n">
-        <v>16.69459872410704</v>
+        <v>2.712872292667394</v>
       </c>
       <c r="E2" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F2" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.8706863527169</v>
+        <v>6.478986532316497</v>
       </c>
       <c r="D3" t="n">
-        <v>20.48740626141664</v>
+        <v>3.329203517480204</v>
       </c>
       <c r="E3" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F3" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>28.70923023637041</v>
+        <v>4.665249913410191</v>
       </c>
       <c r="D4" t="n">
-        <v>32.87184452150991</v>
+        <v>5.341674734745361</v>
       </c>
       <c r="E4" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F4" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>38.63721648952088</v>
+        <v>6.278547679547144</v>
       </c>
       <c r="D5" t="n">
-        <v>25.61104406688281</v>
+        <v>4.161794660868456</v>
       </c>
       <c r="E5" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F5" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.38053952164118</v>
+        <v>7.211837672266692</v>
       </c>
       <c r="D6" t="n">
-        <v>40.75305168426283</v>
+        <v>6.62237089869271</v>
       </c>
       <c r="E6" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F6" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.9755936364667</v>
+        <v>10.55853396592584</v>
       </c>
       <c r="D7" t="n">
-        <v>60.53521070899148</v>
+        <v>9.836971740211116</v>
       </c>
       <c r="E7" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F7" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.41014297819163</v>
+        <v>8.51664823395614</v>
       </c>
       <c r="D8" t="n">
-        <v>46.98551148789866</v>
+        <v>7.635145616783533</v>
       </c>
       <c r="E8" t="n">
-        <v>11.28967996856389</v>
+        <v>1.834572994891632</v>
       </c>
       <c r="F8" t="n">
-        <v>14.47668465053913</v>
+        <v>2.352461255712609</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
